--- a/new-info3/web.xlsx
+++ b/new-info3/web.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12840" windowHeight="7110"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>domain</t>
   </si>
@@ -43,34 +43,16 @@
     <t>color2</t>
   </si>
   <si>
-    <t>perambulate.top</t>
+    <t>read.defeasance.site</t>
   </si>
   <si>
-    <t>#eba46f</t>
+    <t>#92cff4</t>
   </si>
   <si>
-    <t>sesquipedalian.fun</t>
+    <t>sec.defeasance.site</t>
   </si>
   <si>
-    <t>#c2849f</t>
-  </si>
-  <si>
-    <t>moseyquaff.fun</t>
-  </si>
-  <si>
-    <t>#746097</t>
-  </si>
-  <si>
-    <t>fremitus.site</t>
-  </si>
-  <si>
-    <t>#dc7067</t>
-  </si>
-  <si>
-    <t>susurrate.site</t>
-  </si>
-  <si>
-    <t>#f0cfe3</t>
+    <t>#ba7ac7</t>
   </si>
 </sst>
 </file>
@@ -83,7 +65,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,6 +77,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -248,7 +236,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -263,19 +251,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEBA46F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2849F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF746097"/>
+        <fgColor rgb="FF92CFF4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA7AC7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,133 +586,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="37" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -744,19 +726,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1073,7 +1055,7 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1107,37 +1089,17 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="A4" s="5"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>13</v>
-      </c>
+      <c r="A6" s="5"/>
+      <c r="B6" s="7"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="perambulate.top"/>
-    <hyperlink ref="A3" r:id="rId2" display="sesquipedalian.fun"/>
-    <hyperlink ref="A4" r:id="rId3" display="moseyquaff.fun"/>
-    <hyperlink ref="A5" r:id="rId4" display="fremitus.site"/>
-    <hyperlink ref="A6" r:id="rId5" display="susurrate.site"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
